--- a/demo_data/synthetic/P09_Walmart_Context_Exceptions_SYNTHETIC.xlsx
+++ b/demo_data/synthetic/P09_Walmart_Context_Exceptions_SYNTHETIC.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R04e925a842584ac9"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R87ab0f721b124dde"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -14,9 +14,9 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <x:styleSheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:numFmts count="1">
-    <x:numFmt numFmtId="200" formatCode="#,##0"/>
+    <x:numFmt numFmtId="200" formatCode="yyyy-mm-dd"/>
   </x:numFmts>
-  <x:fonts count="3">
+  <x:fonts count="2">
     <x:font>
       <x:sz val="11"/>
       <x:name val="Carlito"/>
@@ -27,14 +27,8 @@
       <x:color rgb="FFFFFFFF"/>
       <x:name val="Carlito"/>
     </x:font>
-    <x:font>
-      <x:b/>
-      <x:sz val="11"/>
-      <x:color rgb="FF6F4B00"/>
-      <x:name val="Carlito"/>
-    </x:font>
   </x:fonts>
-  <x:fills count="4">
+  <x:fills count="3">
     <x:fill>
       <x:patternFill patternType="none"/>
     </x:fill>
@@ -43,85 +37,147 @@
     </x:fill>
     <x:fill>
       <x:patternFill patternType="solid">
-        <x:fgColor rgb="FF174F3B"/>
-      </x:patternFill>
-    </x:fill>
-    <x:fill>
-      <x:patternFill patternType="solid">
-        <x:fgColor rgb="FFFFF0C9"/>
+        <x:fgColor rgb="FF17365D"/>
       </x:patternFill>
     </x:fill>
   </x:fills>
-  <x:borders count="4">
+  <x:borders count="10">
     <x:border/>
     <x:border>
+      <x:right style="thin">
+        <x:color rgb="FFD9E0DC"/>
+      </x:right>
       <x:bottom style="thin">
-        <x:color rgb="FFE0E3DE"/>
+        <x:color rgb="FFD9E0DC"/>
       </x:bottom>
     </x:border>
     <x:border>
+      <x:left style="thin">
+        <x:color rgb="FFD9E0DC"/>
+      </x:left>
+      <x:right style="thin">
+        <x:color rgb="FFD9E0DC"/>
+      </x:right>
+      <x:bottom style="thin">
+        <x:color rgb="FFD9E0DC"/>
+      </x:bottom>
+    </x:border>
+    <x:border>
+      <x:left style="thin">
+        <x:color rgb="FFD9E0DC"/>
+      </x:left>
+      <x:bottom style="thin">
+        <x:color rgb="FFD9E0DC"/>
+      </x:bottom>
+    </x:border>
+    <x:border>
+      <x:right style="thin">
+        <x:color rgb="FFD9E0DC"/>
+      </x:right>
       <x:top style="thin">
-        <x:color rgb="FFE0E3DE"/>
+        <x:color rgb="FFD9E0DC"/>
       </x:top>
       <x:bottom style="thin">
-        <x:color rgb="FFE0E3DE"/>
+        <x:color rgb="FFD9E0DC"/>
       </x:bottom>
     </x:border>
     <x:border>
+      <x:left style="thin">
+        <x:color rgb="FFD9E0DC"/>
+      </x:left>
+      <x:right style="thin">
+        <x:color rgb="FFD9E0DC"/>
+      </x:right>
       <x:top style="thin">
-        <x:color rgb="FFE0E3DE"/>
+        <x:color rgb="FFD9E0DC"/>
       </x:top>
       <x:bottom style="thin">
-        <x:color rgb="FFC8CDC7"/>
+        <x:color rgb="FFD9E0DC"/>
       </x:bottom>
+    </x:border>
+    <x:border>
+      <x:left style="thin">
+        <x:color rgb="FFD9E0DC"/>
+      </x:left>
+      <x:top style="thin">
+        <x:color rgb="FFD9E0DC"/>
+      </x:top>
+      <x:bottom style="thin">
+        <x:color rgb="FFD9E0DC"/>
+      </x:bottom>
+    </x:border>
+    <x:border>
+      <x:right style="thin">
+        <x:color rgb="FFD9E0DC"/>
+      </x:right>
+      <x:top style="thin">
+        <x:color rgb="FFD9E0DC"/>
+      </x:top>
+    </x:border>
+    <x:border>
+      <x:left style="thin">
+        <x:color rgb="FFD9E0DC"/>
+      </x:left>
+      <x:right style="thin">
+        <x:color rgb="FFD9E0DC"/>
+      </x:right>
+      <x:top style="thin">
+        <x:color rgb="FFD9E0DC"/>
+      </x:top>
+    </x:border>
+    <x:border>
+      <x:left style="thin">
+        <x:color rgb="FFD9E0DC"/>
+      </x:left>
+      <x:top style="thin">
+        <x:color rgb="FFD9E0DC"/>
+      </x:top>
     </x:border>
   </x:borders>
   <x:cellStyleXfs count="1">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </x:cellStyleXfs>
-  <x:cellXfs count="14">
+  <x:cellXfs count="19">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <x:xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment wrapText="1"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment vertical="center" wrapText="1"/>
-    </x:xf>
     <x:xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment vertical="center" wrapText="1"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <x:xf numFmtId="0" fontId="0" fillId="3" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <x:xf numFmtId="0" fontId="0" fillId="3" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <x:xf numFmtId="0" fontId="2" fillId="3" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <x:xf numFmtId="0" fontId="2" fillId="3" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <x:xf numFmtId="200" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <x:xf numFmtId="200" fontId="0" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="1" fillId="2" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="200" fontId="0" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="200" fontId="0" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
   </x:cellXfs>
   <x:cellStyles count="1">
     <x:cellStyle name="Normal" xfId="0"/>
   </x:cellStyles>
 </x:styleSheet>
-</file>
-
-<file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="T_P09WalmartContextExc" displayName="T_P09WalmartContextExc" ref="A1:I4" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
-  <x:tableColumns count="9">
-    <x:tableColumn id="1" name="walmart_week"/>
-    <x:tableColumn id="2" name="vendor_stock_id"/>
-    <x:tableColumn id="3" name="event_code"/>
-    <x:tableColumn id="4" name="context_type"/>
-    <x:tableColumn id="5" name="explanation"/>
-    <x:tableColumn id="6" name="required_action"/>
-    <x:tableColumn id="7" name="approved_buffer_quantity"/>
-    <x:tableColumn id="8" name="status"/>
-    <x:tableColumn id="9" name="data_classification"/>
-  </x:tableColumns>
-  <x:tableStyleInfo name="TableStyleMedium4" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
-</x:table>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -319,19 +375,25 @@
 <x:worksheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
-    <x:col min="1" max="1" width="17" hidden="0" customWidth="1"/>
-    <x:col min="2" max="2" width="17" hidden="0" customWidth="1"/>
+    <x:col min="1" max="1" width="15" hidden="0" customWidth="1"/>
+    <x:col min="2" max="2" width="18" hidden="0" customWidth="1"/>
     <x:col min="3" max="3" width="14" hidden="0" customWidth="1"/>
-    <x:col min="4" max="4" width="14" hidden="0" customWidth="1"/>
-    <x:col min="5" max="5" width="72" hidden="0" customWidth="1"/>
-    <x:col min="6" max="6" width="72" hidden="0" customWidth="1"/>
-    <x:col min="7" max="7" width="17" hidden="0" customWidth="1"/>
+    <x:col min="4" max="4" width="15" hidden="0" customWidth="1"/>
+    <x:col min="5" max="5" width="36" hidden="0" customWidth="1"/>
+    <x:col min="6" max="6" width="36" hidden="0" customWidth="1"/>
+    <x:col min="7" max="7" width="27" hidden="0" customWidth="1"/>
     <x:col min="8" max="8" width="14" hidden="0" customWidth="1"/>
-    <x:col min="9" max="9" width="52" hidden="0" customWidth="1"/>
+    <x:col min="9" max="9" width="19" hidden="0" customWidth="1"/>
+    <x:col min="10" max="10" width="26" hidden="0" customWidth="1"/>
+    <x:col min="11" max="11" width="19" hidden="0" customWidth="1"/>
+    <x:col min="12" max="12" width="22" hidden="0" customWidth="1"/>
+    <x:col min="13" max="13" width="28" hidden="0" customWidth="1"/>
+    <x:col min="14" max="14" width="31" hidden="0" customWidth="1"/>
+    <x:col min="15" max="15" width="42" hidden="0" customWidth="1"/>
   </x:cols>
   <x:sheetData>
-    <x:row r="1">
-      <x:c r="A1" s="5" t="str">
+    <x:row r="1" ht="15" hidden="0" customHeight="1">
+      <x:c r="A1" s="4" t="str">
         <x:v>walmart_week</x:v>
       </x:c>
       <x:c r="B1" s="5" t="str">
@@ -356,100 +418,169 @@
         <x:v>status</x:v>
       </x:c>
       <x:c r="I1" s="5" t="str">
+        <x:v>modular_set_week</x:v>
+      </x:c>
+      <x:c r="J1" s="5" t="str">
+        <x:v>system_order_start_week</x:v>
+      </x:c>
+      <x:c r="K1" s="5" t="str">
+        <x:v>modular_set_date</x:v>
+      </x:c>
+      <x:c r="L1" s="5" t="str">
+        <x:v>traited_store_count</x:v>
+      </x:c>
+      <x:c r="M1" s="5" t="str">
+        <x:v>prior_traited_store_count</x:v>
+      </x:c>
+      <x:c r="N1" s="5" t="str">
+        <x:v>initial_fill_units_per_store</x:v>
+      </x:c>
+      <x:c r="O1" s="6" t="str">
         <x:v>data_classification</x:v>
       </x:c>
     </x:row>
-    <x:row r="2">
-      <x:c r="A2" s="6" t="str">
+    <x:row r="2" ht="42" hidden="0" customHeight="1">
+      <x:c r="A2" s="7" t="str">
         <x:v>202630</x:v>
       </x:c>
-      <x:c r="B2" s="6" t="str">
+      <x:c r="B2" s="8" t="str">
         <x:v>DEMO-SURPLUS</x:v>
       </x:c>
-      <x:c r="C2" s="6" t="str">
+      <x:c r="C2" s="8" t="str">
         <x:v>BASE</x:v>
       </x:c>
-      <x:c r="D2" s="6" t="str">
+      <x:c r="D2" s="8" t="str">
         <x:v>NORMAL</x:v>
       </x:c>
-      <x:c r="E2" s="6" t="str">
+      <x:c r="E2" s="13" t="str">
         <x:v>Demand and confirmed commitments remain within covered supply.</x:v>
       </x:c>
-      <x:c r="F2" s="6" t="str">
+      <x:c r="F2" s="13" t="str">
         <x:v>Continue weekly monitoring.</x:v>
       </x:c>
-      <x:c r="G2" s="12" t="n">
+      <x:c r="G2" s="8" t="n">
         <x:v>100</x:v>
       </x:c>
-      <x:c r="H2" s="6" t="str">
+      <x:c r="H2" s="8" t="str">
         <x:v>CLEAR</x:v>
       </x:c>
-      <x:c r="I2" s="10" t="str">
+      <x:c r="I2" s="8" t="str">
+        <x:v>202638</x:v>
+      </x:c>
+      <x:c r="J2" s="8" t="str">
+        <x:v>202632</x:v>
+      </x:c>
+      <x:c r="K2" s="15" t="n">
+        <x:v>46283</x:v>
+      </x:c>
+      <x:c r="L2" s="8" t="n">
+        <x:v>1206</x:v>
+      </x:c>
+      <x:c r="M2" s="8" t="n">
+        <x:v>996</x:v>
+      </x:c>
+      <x:c r="N2" s="8" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="O2" s="17" t="str">
         <x:v>SYNTHETIC DEMONSTRATION DATA - NOT FOR OPERATIONAL USE</x:v>
       </x:c>
     </x:row>
-    <x:row r="3">
-      <x:c r="A3" s="6" t="str">
+    <x:row r="3" ht="42" hidden="0" customHeight="1">
+      <x:c r="A3" s="7" t="str">
         <x:v>202630</x:v>
       </x:c>
-      <x:c r="B3" s="6" t="str">
+      <x:c r="B3" s="8" t="str">
         <x:v>DEMO-SHORTAGE</x:v>
       </x:c>
-      <x:c r="C3" s="6" t="str">
+      <x:c r="C3" s="8" t="str">
         <x:v>DISPLAY</x:v>
       </x:c>
-      <x:c r="D3" s="6" t="str">
+      <x:c r="D3" s="8" t="str">
         <x:v>PROMOTION</x:v>
       </x:c>
-      <x:c r="E3" s="6" t="str">
+      <x:c r="E3" s="13" t="str">
         <x:v>Illustrative display activity raises near-term demand above covered supply.</x:v>
       </x:c>
-      <x:c r="F3" s="6" t="str">
+      <x:c r="F3" s="13" t="str">
         <x:v>Investigate replenishment and production options before authorization.</x:v>
       </x:c>
-      <x:c r="G3" s="12" t="n">
+      <x:c r="G3" s="8" t="n">
         <x:v>100</x:v>
       </x:c>
-      <x:c r="H3" s="6" t="str">
+      <x:c r="H3" s="8" t="str">
         <x:v>INVESTIGATE</x:v>
       </x:c>
-      <x:c r="I3" s="10" t="str">
+      <x:c r="I3" s="8" t="str">
+        <x:v>202638</x:v>
+      </x:c>
+      <x:c r="J3" s="8" t="str">
+        <x:v>202632</x:v>
+      </x:c>
+      <x:c r="K3" s="15" t="n">
+        <x:v>46283</x:v>
+      </x:c>
+      <x:c r="L3" s="8" t="n">
+        <x:v>1206</x:v>
+      </x:c>
+      <x:c r="M3" s="8" t="n">
+        <x:v>996</x:v>
+      </x:c>
+      <x:c r="N3" s="8" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="O3" s="17" t="str">
         <x:v>SYNTHETIC DEMONSTRATION DATA - NOT FOR OPERATIONAL USE</x:v>
       </x:c>
     </x:row>
-    <x:row r="4">
-      <x:c r="A4" s="7" t="str">
+    <x:row r="4" ht="42" hidden="0" customHeight="1">
+      <x:c r="A4" s="10" t="str">
         <x:v>202630</x:v>
       </x:c>
-      <x:c r="B4" s="7" t="str">
+      <x:c r="B4" s="11" t="str">
         <x:v>DEMO-LATE</x:v>
       </x:c>
-      <x:c r="C4" s="7" t="str">
+      <x:c r="C4" s="11" t="str">
         <x:v>NEW-MOD</x:v>
       </x:c>
-      <x:c r="D4" s="7" t="str">
+      <x:c r="D4" s="11" t="str">
         <x:v>MODULAR</x:v>
       </x:c>
-      <x:c r="E4" s="7" t="str">
+      <x:c r="E4" s="14" t="str">
         <x:v>Illustrative modular timing requires inventory before the inbound becomes available.</x:v>
       </x:c>
-      <x:c r="F4" s="7" t="str">
+      <x:c r="F4" s="14" t="str">
         <x:v>Do not count late inbound against the current MABD; escalate timing.</x:v>
       </x:c>
-      <x:c r="G4" s="13" t="n">
+      <x:c r="G4" s="11" t="n">
         <x:v>50</x:v>
       </x:c>
-      <x:c r="H4" s="7" t="str">
+      <x:c r="H4" s="11" t="str">
         <x:v>INVESTIGATE</x:v>
       </x:c>
       <x:c r="I4" s="11" t="str">
+        <x:v>202638</x:v>
+      </x:c>
+      <x:c r="J4" s="11" t="str">
+        <x:v>202632</x:v>
+      </x:c>
+      <x:c r="K4" s="16" t="n">
+        <x:v>46283</x:v>
+      </x:c>
+      <x:c r="L4" s="11" t="n">
+        <x:v>1206</x:v>
+      </x:c>
+      <x:c r="M4" s="11" t="n">
+        <x:v>996</x:v>
+      </x:c>
+      <x:c r="N4" s="11" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="O4" s="18" t="str">
         <x:v>SYNTHETIC DEMONSTRATION DATA - NOT FOR OPERATIONAL USE</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Ra3cf7a46431145da"/>
-  </x:tableParts>
 </x:worksheet>
 </file>